--- a/Excel/MonsterModelConfig.xlsx
+++ b/Excel/MonsterModelConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="15">
   <si>
     <t>ID</t>
   </si>
@@ -36,28 +36,13 @@
     <t>Name</t>
   </si>
   <si>
-    <t>AttrRate</t>
+    <t>AtrRate</t>
   </si>
   <si>
     <t>HpRate</t>
   </si>
   <si>
     <t>DefRate</t>
-  </si>
-  <si>
-    <t>DropRate</t>
-  </si>
-  <si>
-    <t>RewardRate</t>
-  </si>
-  <si>
-    <t>CountRate</t>
-  </si>
-  <si>
-    <t>SkillList</t>
-  </si>
-  <si>
-    <t>Desc</t>
   </si>
   <si>
     <t>Id</t>
@@ -72,16 +57,19 @@
     <t>double</t>
   </si>
   <si>
-    <t>int[]</t>
-  </si>
-  <si>
-    <t>暗殿</t>
+    <t>关卡</t>
   </si>
   <si>
     <t>AttrList</t>
   </si>
   <si>
     <t>AttrValueList</t>
+  </si>
+  <si>
+    <t>SkillList</t>
+  </si>
+  <si>
+    <t>int[]</t>
   </si>
   <si>
     <t>long[]</t>
@@ -717,15 +705,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1045,8 +1031,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <dimension ref="A1:K53"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
@@ -1055,17 +1041,14 @@
     <col min="5" max="5" width="15.7333333333333" style="2" customWidth="1"/>
     <col min="6" max="6" width="13.525" style="2" customWidth="1"/>
     <col min="7" max="7" width="13.8166666666667" style="2" customWidth="1"/>
-    <col min="8" max="8" width="12.0583333333333" style="2" customWidth="1"/>
-    <col min="9" max="10" width="10" style="2" customWidth="1"/>
-    <col min="11" max="12" width="20.75" style="2" customWidth="1"/>
-    <col min="13" max="13" width="46" style="2" customWidth="1"/>
-    <col min="14" max="14" width="13.625" style="2" customWidth="1"/>
-    <col min="15" max="15" width="8.125" style="2" customWidth="1"/>
-    <col min="16" max="16" width="9.625" style="2" customWidth="1"/>
-    <col min="17" max="16384" width="9" style="2"/>
+    <col min="8" max="8" width="46" style="2" customWidth="1"/>
+    <col min="9" max="9" width="13.625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="8.125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="9.625" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:16">
+    <row r="1" s="1" customFormat="1" spans="1:11">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="E1" s="2"/>
@@ -1075,13 +1058,8 @@
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:16">
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:11">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="E2" s="2"/>
@@ -1091,13 +1069,8 @@
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:16">
+    </row>
+    <row r="3" s="1" customFormat="1" ht="13.5" spans="1:11">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
@@ -1115,31 +1088,16 @@
       <c r="G3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
-      <c r="P3" s="2"/>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:16">
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="13.5" spans="1:11">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>1</v>
@@ -1153,657 +1111,383 @@
       <c r="G4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2"/>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:16">
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="13.5" spans="1:11">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2"/>
-    </row>
-    <row r="6" ht="24" customHeight="1" spans="3:12">
+        <v>8</v>
+      </c>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="1:11">
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>0.3</v>
-      </c>
-      <c r="I6">
-        <v>0.5</v>
-      </c>
-      <c r="J6">
-        <v>0.2</v>
-      </c>
-      <c r="K6"/>
-      <c r="L6"/>
-    </row>
-    <row r="7" ht="24" customHeight="1" spans="3:12">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1" spans="1:11">
       <c r="C7"/>
       <c r="D7"/>
       <c r="E7"/>
       <c r="F7"/>
       <c r="G7"/>
-      <c r="H7"/>
-      <c r="I7"/>
-      <c r="J7"/>
-      <c r="K7"/>
-      <c r="L7"/>
-    </row>
-    <row r="8" ht="24" customHeight="1" spans="3:12">
+    </row>
+    <row r="8" ht="24" customHeight="1" spans="1:11">
       <c r="C8"/>
       <c r="D8"/>
       <c r="E8"/>
       <c r="F8"/>
       <c r="G8"/>
-      <c r="H8"/>
-      <c r="I8"/>
-      <c r="J8"/>
-      <c r="K8"/>
-      <c r="L8"/>
-    </row>
-    <row r="9" ht="24" customHeight="1" spans="3:12">
+    </row>
+    <row r="9" ht="24" customHeight="1" spans="1:11">
       <c r="C9"/>
       <c r="D9"/>
       <c r="E9"/>
       <c r="F9"/>
       <c r="G9"/>
-      <c r="H9"/>
-      <c r="I9"/>
-      <c r="J9"/>
-      <c r="K9"/>
-      <c r="L9"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" spans="3:12">
+    </row>
+    <row r="10" ht="24" customHeight="1" spans="1:11">
       <c r="C10"/>
       <c r="D10"/>
       <c r="E10"/>
       <c r="F10"/>
       <c r="G10"/>
-      <c r="H10"/>
-      <c r="I10"/>
-      <c r="J10"/>
-      <c r="K10"/>
-      <c r="L10"/>
-    </row>
-    <row r="11" ht="24" customHeight="1" spans="3:12">
+    </row>
+    <row r="11" ht="24" customHeight="1" spans="1:11">
       <c r="C11"/>
       <c r="D11"/>
       <c r="E11"/>
       <c r="F11"/>
       <c r="G11"/>
-      <c r="H11"/>
-      <c r="I11"/>
-      <c r="J11"/>
-      <c r="K11"/>
-      <c r="L11"/>
-    </row>
-    <row r="12" ht="24" customHeight="1" spans="3:12">
+    </row>
+    <row r="12" ht="24" customHeight="1" spans="1:11">
       <c r="C12"/>
       <c r="D12"/>
       <c r="E12"/>
       <c r="F12"/>
       <c r="G12"/>
-      <c r="H12"/>
-      <c r="I12"/>
-      <c r="J12"/>
-      <c r="K12"/>
-      <c r="L12"/>
-    </row>
-    <row r="13" ht="24" customHeight="1" spans="3:12">
+    </row>
+    <row r="13" ht="24" customHeight="1" spans="1:11">
       <c r="C13"/>
       <c r="D13"/>
       <c r="E13"/>
       <c r="F13"/>
       <c r="G13"/>
-      <c r="H13"/>
-      <c r="I13"/>
-      <c r="J13"/>
-      <c r="K13"/>
-      <c r="L13"/>
-    </row>
-    <row r="14" ht="24" customHeight="1" spans="3:12">
+    </row>
+    <row r="14" ht="24" customHeight="1" spans="1:11">
       <c r="C14"/>
       <c r="D14"/>
       <c r="E14"/>
       <c r="F14"/>
       <c r="G14"/>
-      <c r="H14"/>
-      <c r="I14"/>
-      <c r="J14"/>
-      <c r="K14"/>
-      <c r="L14"/>
-    </row>
-    <row r="15" ht="24" customHeight="1" spans="3:12">
+    </row>
+    <row r="15" ht="24" customHeight="1" spans="1:11">
       <c r="C15"/>
       <c r="D15"/>
       <c r="E15"/>
       <c r="F15"/>
       <c r="G15"/>
-      <c r="H15"/>
-      <c r="I15"/>
-      <c r="J15"/>
-      <c r="K15"/>
-      <c r="L15"/>
-    </row>
-    <row r="16" ht="24" customHeight="1" spans="3:12">
+    </row>
+    <row r="16" ht="24" customHeight="1" spans="1:11">
       <c r="C16"/>
       <c r="D16"/>
       <c r="E16"/>
       <c r="F16"/>
       <c r="G16"/>
-      <c r="H16"/>
-      <c r="I16"/>
-      <c r="J16"/>
-      <c r="K16"/>
-      <c r="L16"/>
-    </row>
-    <row r="17" ht="24" customHeight="1" spans="3:12">
+    </row>
+    <row r="17" ht="24" customHeight="1" spans="3:7">
       <c r="C17"/>
       <c r="D17"/>
       <c r="E17"/>
       <c r="F17"/>
       <c r="G17"/>
-      <c r="H17"/>
-      <c r="I17"/>
-      <c r="J17"/>
-      <c r="K17"/>
-      <c r="L17"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" spans="3:12">
+    </row>
+    <row r="18" ht="24" customHeight="1" spans="3:7">
       <c r="C18"/>
       <c r="D18"/>
       <c r="E18"/>
       <c r="F18"/>
       <c r="G18"/>
-      <c r="H18"/>
-      <c r="I18"/>
-      <c r="J18"/>
-      <c r="K18" s="4"/>
-      <c r="L18"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" spans="3:12">
+    </row>
+    <row r="19" ht="24" customHeight="1" spans="3:7">
       <c r="C19"/>
       <c r="D19"/>
       <c r="E19"/>
       <c r="F19"/>
       <c r="G19"/>
-      <c r="H19"/>
-      <c r="I19"/>
-      <c r="J19"/>
-      <c r="K19"/>
-      <c r="L19"/>
-    </row>
-    <row r="20" ht="24" customHeight="1" spans="3:12">
+    </row>
+    <row r="20" ht="24" customHeight="1" spans="3:7">
       <c r="C20"/>
       <c r="D20"/>
       <c r="E20"/>
       <c r="F20"/>
       <c r="G20"/>
-      <c r="H20"/>
-      <c r="I20"/>
-      <c r="J20"/>
-      <c r="K20"/>
-      <c r="L20"/>
-    </row>
-    <row r="21" ht="24" customHeight="1" spans="3:12">
+    </row>
+    <row r="21" ht="24" customHeight="1" spans="3:7">
       <c r="C21"/>
       <c r="D21"/>
       <c r="E21"/>
       <c r="F21"/>
       <c r="G21"/>
-      <c r="H21"/>
-      <c r="I21"/>
-      <c r="J21"/>
-      <c r="K21"/>
-      <c r="L21"/>
-    </row>
-    <row r="22" ht="24" customHeight="1" spans="3:12">
+    </row>
+    <row r="22" ht="24" customHeight="1" spans="3:7">
       <c r="C22"/>
       <c r="D22"/>
       <c r="E22"/>
       <c r="F22"/>
       <c r="G22"/>
-      <c r="H22"/>
-      <c r="I22"/>
-      <c r="J22"/>
-      <c r="K22"/>
-      <c r="L22"/>
-    </row>
-    <row r="23" ht="24" customHeight="1" spans="3:12">
+    </row>
+    <row r="23" ht="24" customHeight="1" spans="3:7">
       <c r="C23"/>
       <c r="D23"/>
       <c r="E23"/>
       <c r="F23"/>
       <c r="G23"/>
-      <c r="H23"/>
-      <c r="I23"/>
-      <c r="J23"/>
-      <c r="K23"/>
-      <c r="L23"/>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="3:12">
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="3:7">
       <c r="C24"/>
       <c r="D24"/>
       <c r="E24"/>
       <c r="F24"/>
       <c r="G24"/>
-      <c r="H24"/>
-      <c r="I24"/>
-      <c r="J24"/>
-      <c r="K24"/>
-      <c r="L24"/>
-    </row>
-    <row r="25" ht="24" customHeight="1" spans="3:12">
+    </row>
+    <row r="25" ht="24" customHeight="1" spans="3:7">
       <c r="C25"/>
       <c r="D25"/>
       <c r="E25"/>
       <c r="F25"/>
       <c r="G25"/>
-      <c r="H25"/>
-      <c r="I25"/>
-      <c r="J25"/>
-      <c r="K25"/>
-      <c r="L25"/>
-    </row>
-    <row r="26" ht="24" customHeight="1" spans="3:12">
+    </row>
+    <row r="26" ht="24" customHeight="1" spans="3:7">
       <c r="C26"/>
       <c r="D26"/>
       <c r="E26"/>
       <c r="F26"/>
       <c r="G26"/>
-      <c r="H26"/>
-      <c r="I26"/>
-      <c r="J26"/>
-      <c r="K26"/>
-      <c r="L26"/>
-    </row>
-    <row r="27" ht="24" customHeight="1" spans="3:12">
+    </row>
+    <row r="27" ht="24" customHeight="1" spans="3:7">
       <c r="C27"/>
       <c r="D27"/>
       <c r="E27"/>
       <c r="F27"/>
       <c r="G27"/>
-      <c r="H27"/>
-      <c r="I27"/>
-      <c r="J27"/>
-      <c r="K27"/>
-      <c r="L27"/>
-    </row>
-    <row r="28" ht="24" customHeight="1" spans="3:12">
+    </row>
+    <row r="28" ht="24" customHeight="1" spans="3:7">
       <c r="C28"/>
       <c r="D28"/>
       <c r="E28"/>
       <c r="F28"/>
       <c r="G28"/>
-      <c r="H28"/>
-      <c r="I28"/>
-      <c r="J28"/>
-      <c r="K28"/>
-      <c r="L28"/>
-    </row>
-    <row r="29" ht="24" customHeight="1" spans="3:12">
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="3:7">
       <c r="C29"/>
       <c r="D29"/>
       <c r="E29"/>
       <c r="F29"/>
       <c r="G29"/>
-      <c r="H29"/>
-      <c r="I29"/>
-      <c r="J29"/>
-      <c r="K29"/>
-      <c r="L29"/>
-    </row>
-    <row r="30" ht="24" customHeight="1" spans="3:12">
+    </row>
+    <row r="30" ht="24" customHeight="1" spans="3:7">
       <c r="C30"/>
       <c r="D30"/>
       <c r="E30"/>
       <c r="F30"/>
       <c r="G30"/>
-      <c r="H30"/>
-      <c r="I30"/>
-      <c r="J30"/>
-      <c r="K30"/>
-      <c r="L30"/>
-    </row>
-    <row r="31" ht="24" customHeight="1" spans="3:11">
+    </row>
+    <row r="31" ht="24" customHeight="1" spans="3:7">
       <c r="C31"/>
       <c r="D31"/>
       <c r="E31"/>
       <c r="F31"/>
       <c r="G31"/>
-      <c r="H31"/>
-      <c r="I31"/>
-      <c r="J31"/>
-      <c r="K31"/>
-    </row>
-    <row r="32" ht="24" customHeight="1" spans="3:12">
+    </row>
+    <row r="32" ht="24" customHeight="1" spans="3:7">
       <c r="C32"/>
       <c r="D32"/>
       <c r="E32"/>
       <c r="F32"/>
       <c r="G32"/>
-      <c r="H32"/>
-      <c r="I32"/>
-      <c r="J32"/>
-      <c r="K32"/>
-      <c r="L32" s="5"/>
-    </row>
-    <row r="33" ht="24" customHeight="1" spans="3:11">
+    </row>
+    <row r="33" ht="24" customHeight="1" spans="3:7">
       <c r="C33"/>
       <c r="D33"/>
       <c r="E33"/>
       <c r="F33"/>
       <c r="G33"/>
-      <c r="H33"/>
-      <c r="I33"/>
-      <c r="J33"/>
-      <c r="K33"/>
-    </row>
-    <row r="34" ht="24" customHeight="1" spans="3:12">
+    </row>
+    <row r="34" ht="24" customHeight="1" spans="3:7">
       <c r="C34"/>
       <c r="D34"/>
       <c r="E34"/>
       <c r="F34"/>
       <c r="G34"/>
-      <c r="H34"/>
-      <c r="I34"/>
-      <c r="J34"/>
-      <c r="K34"/>
-      <c r="L34"/>
-    </row>
-    <row r="35" ht="24" customHeight="1" spans="3:12">
+    </row>
+    <row r="35" ht="24" customHeight="1" spans="3:7">
       <c r="C35"/>
       <c r="D35"/>
       <c r="E35"/>
       <c r="F35"/>
       <c r="G35"/>
-      <c r="H35"/>
-      <c r="I35"/>
-      <c r="J35"/>
-      <c r="K35"/>
-      <c r="L35"/>
-    </row>
-    <row r="36" ht="24" customHeight="1" spans="3:12">
+    </row>
+    <row r="36" ht="24" customHeight="1" spans="3:7">
       <c r="C36"/>
       <c r="D36"/>
       <c r="E36"/>
       <c r="F36"/>
       <c r="G36"/>
-      <c r="H36"/>
-      <c r="I36"/>
-      <c r="J36"/>
-      <c r="K36"/>
-      <c r="L36"/>
-    </row>
-    <row r="37" ht="24" customHeight="1" spans="3:12">
+    </row>
+    <row r="37" ht="24" customHeight="1" spans="3:7">
       <c r="C37"/>
       <c r="D37"/>
       <c r="E37"/>
       <c r="F37"/>
       <c r="G37"/>
-      <c r="H37"/>
-      <c r="I37"/>
-      <c r="J37"/>
-      <c r="K37"/>
-      <c r="L37"/>
-    </row>
-    <row r="38" ht="24" customHeight="1" spans="3:12">
+    </row>
+    <row r="38" ht="24" customHeight="1" spans="3:7">
       <c r="C38"/>
       <c r="D38"/>
       <c r="E38"/>
       <c r="F38"/>
       <c r="G38"/>
-      <c r="H38"/>
-      <c r="I38"/>
-      <c r="J38"/>
-      <c r="K38"/>
-      <c r="L38"/>
-    </row>
-    <row r="39" ht="24" customHeight="1" spans="3:12">
+    </row>
+    <row r="39" ht="24" customHeight="1" spans="3:7">
       <c r="C39"/>
       <c r="D39"/>
       <c r="E39"/>
       <c r="F39"/>
       <c r="G39"/>
-      <c r="H39"/>
-      <c r="I39"/>
-      <c r="J39"/>
-      <c r="K39"/>
-      <c r="L39"/>
-    </row>
-    <row r="40" ht="24" customHeight="1" spans="3:12">
+    </row>
+    <row r="40" ht="24" customHeight="1" spans="3:7">
       <c r="C40"/>
       <c r="D40"/>
       <c r="E40"/>
       <c r="F40"/>
       <c r="G40"/>
-      <c r="H40"/>
-      <c r="I40"/>
-      <c r="J40"/>
-      <c r="K40"/>
-      <c r="L40"/>
-    </row>
-    <row r="41" ht="24" customHeight="1" spans="3:12">
+    </row>
+    <row r="41" ht="24" customHeight="1" spans="3:7">
       <c r="C41"/>
       <c r="D41"/>
       <c r="E41"/>
       <c r="F41"/>
       <c r="G41"/>
-      <c r="H41"/>
-      <c r="I41"/>
-      <c r="J41"/>
-      <c r="K41"/>
-      <c r="L41"/>
-    </row>
-    <row r="42" ht="24" customHeight="1" spans="3:12">
+    </row>
+    <row r="42" ht="24" customHeight="1" spans="3:7">
       <c r="C42"/>
       <c r="D42"/>
       <c r="E42"/>
       <c r="F42"/>
       <c r="G42"/>
-      <c r="H42"/>
-      <c r="I42"/>
-      <c r="J42"/>
-      <c r="K42"/>
-      <c r="L42"/>
-    </row>
-    <row r="43" ht="24" customHeight="1" spans="3:12">
+    </row>
+    <row r="43" ht="24" customHeight="1" spans="3:7">
       <c r="C43"/>
       <c r="D43"/>
       <c r="E43"/>
       <c r="F43"/>
       <c r="G43"/>
-      <c r="H43"/>
-      <c r="I43"/>
-      <c r="J43"/>
-      <c r="K43"/>
-      <c r="L43"/>
-    </row>
-    <row r="44" ht="24" customHeight="1" spans="3:12">
+    </row>
+    <row r="44" ht="24" customHeight="1" spans="3:7">
       <c r="C44"/>
       <c r="D44"/>
       <c r="E44"/>
       <c r="F44"/>
       <c r="G44"/>
-      <c r="H44"/>
-      <c r="I44"/>
-      <c r="J44"/>
-      <c r="K44"/>
-      <c r="L44"/>
-    </row>
-    <row r="45" ht="24" customHeight="1" spans="3:12">
+    </row>
+    <row r="45" ht="24" customHeight="1" spans="3:7">
       <c r="C45"/>
       <c r="D45"/>
       <c r="E45"/>
       <c r="F45"/>
       <c r="G45"/>
-      <c r="H45"/>
-      <c r="I45"/>
-      <c r="J45"/>
-      <c r="K45"/>
-      <c r="L45"/>
-    </row>
-    <row r="46" ht="24" customHeight="1" spans="3:12">
+    </row>
+    <row r="46" ht="24" customHeight="1" spans="3:7">
       <c r="C46"/>
       <c r="D46"/>
       <c r="E46"/>
       <c r="F46"/>
       <c r="G46"/>
-      <c r="H46"/>
-      <c r="I46"/>
-      <c r="J46"/>
-      <c r="K46"/>
-      <c r="L46"/>
-    </row>
-    <row r="47" ht="24" customHeight="1" spans="3:12">
+    </row>
+    <row r="47" ht="24" customHeight="1" spans="3:7">
       <c r="C47"/>
       <c r="D47"/>
       <c r="E47"/>
       <c r="F47"/>
       <c r="G47"/>
-      <c r="H47"/>
-      <c r="I47"/>
-      <c r="J47"/>
-      <c r="K47"/>
-      <c r="L47"/>
-    </row>
-    <row r="48" ht="24" customHeight="1" spans="3:12">
+    </row>
+    <row r="48" ht="24" customHeight="1" spans="3:7">
       <c r="C48"/>
       <c r="D48"/>
       <c r="E48"/>
       <c r="F48"/>
       <c r="G48"/>
-      <c r="H48"/>
-      <c r="I48"/>
-      <c r="J48"/>
-      <c r="K48"/>
-      <c r="L48"/>
-    </row>
-    <row r="49" ht="24" customHeight="1" spans="3:12">
+    </row>
+    <row r="49" ht="24" customHeight="1" spans="3:7">
       <c r="C49"/>
       <c r="D49"/>
       <c r="E49"/>
       <c r="F49"/>
       <c r="G49"/>
-      <c r="H49"/>
-      <c r="I49"/>
-      <c r="J49"/>
-      <c r="K49"/>
-      <c r="L49"/>
-    </row>
-    <row r="50" ht="24" customHeight="1" spans="3:12">
+    </row>
+    <row r="50" ht="24" customHeight="1" spans="3:7">
       <c r="C50"/>
       <c r="D50"/>
       <c r="E50"/>
       <c r="F50"/>
       <c r="G50"/>
-      <c r="H50"/>
-      <c r="I50"/>
-      <c r="J50"/>
-      <c r="K50"/>
-      <c r="L50"/>
-    </row>
-    <row r="51" ht="24" customHeight="1" spans="3:12">
+    </row>
+    <row r="51" ht="24" customHeight="1" spans="3:7">
       <c r="C51"/>
       <c r="D51"/>
       <c r="E51"/>
       <c r="F51"/>
       <c r="G51"/>
-      <c r="H51"/>
-      <c r="I51"/>
-      <c r="J51"/>
-      <c r="K51"/>
-      <c r="L51"/>
-    </row>
-    <row r="52" ht="24" customHeight="1" spans="3:12">
+    </row>
+    <row r="52" ht="24" customHeight="1" spans="3:7">
       <c r="C52"/>
       <c r="D52"/>
       <c r="E52"/>
       <c r="F52"/>
       <c r="G52"/>
-      <c r="H52"/>
-      <c r="I52"/>
-      <c r="J52"/>
-      <c r="K52"/>
-      <c r="L52"/>
-    </row>
-    <row r="53" ht="24" customHeight="1" spans="3:12">
+    </row>
+    <row r="53" ht="24" customHeight="1" spans="3:7">
       <c r="C53"/>
       <c r="D53"/>
       <c r="E53"/>
       <c r="F53"/>
       <c r="G53"/>
-      <c r="H53"/>
-      <c r="I53"/>
-      <c r="J53"/>
-      <c r="K53"/>
-      <c r="L53"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3 E3 F3 H3 I3 J3 K3 L3 E4 F4 H4 I4 J4 K4 L4 E5 F5 G5 H5 I5 J5 K5 L5 C3:C5 D4:D5 G3:G4" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:G3 C4:D4 E4 F4:G4 C5:G5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -1816,7 +1500,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:O38"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
@@ -1834,7 +1518,7 @@
     <col min="15" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:14">
+    <row r="1" s="1" customFormat="1" spans="1:15">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="E1" s="2"/>
@@ -1848,7 +1532,7 @@
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:14">
+    <row r="2" s="1" customFormat="1" spans="1:15">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="E2" s="2"/>
@@ -1862,7 +1546,7 @@
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:12">
+    <row r="3" s="1" customFormat="1" ht="13.5" spans="1:15">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
@@ -1872,13 +1556,13 @@
         <v>1</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
@@ -1886,23 +1570,23 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:12">
+    <row r="4" s="1" customFormat="1" ht="13.5" spans="1:15">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>1</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
@@ -1910,23 +1594,23 @@
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:12">
+    <row r="5" s="1" customFormat="1" ht="13.5" spans="1:15">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>18</v>
-      </c>
       <c r="G5" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
@@ -1944,7 +1628,7 @@
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
     </row>
-    <row r="7" s="2" customFormat="1" ht="24" customHeight="1" spans="3:9">
+    <row r="7" s="2" customFormat="1" ht="24" customHeight="1" spans="1:15">
       <c r="C7"/>
       <c r="D7"/>
       <c r="E7"/>
@@ -1953,7 +1637,7 @@
       <c r="H7"/>
       <c r="I7"/>
     </row>
-    <row r="8" s="2" customFormat="1" ht="24" customHeight="1" spans="3:9">
+    <row r="8" s="2" customFormat="1" ht="24" customHeight="1" spans="1:15">
       <c r="C8"/>
       <c r="D8"/>
       <c r="E8"/>
@@ -1962,7 +1646,7 @@
       <c r="H8"/>
       <c r="I8"/>
     </row>
-    <row r="9" s="2" customFormat="1" ht="24" customHeight="1" spans="3:9">
+    <row r="9" s="2" customFormat="1" ht="24" customHeight="1" spans="1:15">
       <c r="C9"/>
       <c r="D9"/>
       <c r="E9"/>
@@ -1971,7 +1655,7 @@
       <c r="H9"/>
       <c r="I9"/>
     </row>
-    <row r="10" s="2" customFormat="1" ht="24" customHeight="1" spans="3:9">
+    <row r="10" s="2" customFormat="1" ht="24" customHeight="1" spans="1:15">
       <c r="C10"/>
       <c r="D10"/>
       <c r="E10"/>
@@ -1980,7 +1664,7 @@
       <c r="H10"/>
       <c r="I10"/>
     </row>
-    <row r="11" s="2" customFormat="1" ht="24" customHeight="1" spans="3:9">
+    <row r="11" s="2" customFormat="1" ht="24" customHeight="1" spans="1:15">
       <c r="C11"/>
       <c r="D11"/>
       <c r="E11"/>
@@ -1989,7 +1673,7 @@
       <c r="H11"/>
       <c r="I11"/>
     </row>
-    <row r="12" s="2" customFormat="1" ht="24" customHeight="1" spans="3:9">
+    <row r="12" s="2" customFormat="1" ht="24" customHeight="1" spans="1:15">
       <c r="C12"/>
       <c r="D12"/>
       <c r="E12"/>
@@ -1998,7 +1682,7 @@
       <c r="H12"/>
       <c r="I12"/>
     </row>
-    <row r="13" s="2" customFormat="1" ht="24" customHeight="1" spans="3:9">
+    <row r="13" s="2" customFormat="1" ht="24" customHeight="1" spans="1:15">
       <c r="C13"/>
       <c r="D13"/>
       <c r="E13"/>
@@ -2007,7 +1691,7 @@
       <c r="H13"/>
       <c r="I13"/>
     </row>
-    <row r="14" s="2" customFormat="1" ht="24" customHeight="1" spans="3:9">
+    <row r="14" s="2" customFormat="1" ht="24" customHeight="1" spans="1:15">
       <c r="C14"/>
       <c r="D14"/>
       <c r="E14"/>
@@ -2016,7 +1700,7 @@
       <c r="H14"/>
       <c r="I14"/>
     </row>
-    <row r="15" s="2" customFormat="1" ht="24" customHeight="1" spans="3:9">
+    <row r="15" s="2" customFormat="1" ht="24" customHeight="1" spans="1:15">
       <c r="C15"/>
       <c r="D15"/>
       <c r="E15"/>
@@ -2025,7 +1709,7 @@
       <c r="H15"/>
       <c r="I15"/>
     </row>
-    <row r="16" s="2" customFormat="1" ht="24" customHeight="1" spans="3:9">
+    <row r="16" s="2" customFormat="1" ht="24" customHeight="1" spans="1:15">
       <c r="C16"/>
       <c r="D16"/>
       <c r="E16"/>
@@ -2234,7 +1918,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3 E3:G3 E4 F4 G4 E5 F5 G5 C3:C5 D4:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:G5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
